--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0001T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.41046573469169</v>
+        <v>4.941700681887401</v>
       </c>
       <c r="D2" t="n">
-        <v>72.14107967591053</v>
+        <v>11.72292544733546</v>
       </c>
       <c r="E2" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F2" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.66385107844859</v>
+        <v>3.195375800247896</v>
       </c>
       <c r="D3" t="n">
-        <v>61.67030576480592</v>
+        <v>10.02142468678096</v>
       </c>
       <c r="E3" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F3" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>56.98049618523849</v>
+        <v>9.259330630101255</v>
       </c>
       <c r="D4" t="n">
-        <v>43.64750198959257</v>
+        <v>7.092719073308793</v>
       </c>
       <c r="E4" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F4" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.35857169358858</v>
+        <v>7.045767900208144</v>
       </c>
       <c r="D5" t="n">
-        <v>44.09832850229804</v>
+        <v>7.165978381623431</v>
       </c>
       <c r="E5" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F5" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>70.67629164048897</v>
+        <v>11.48489739157946</v>
       </c>
       <c r="D6" t="n">
-        <v>85.05531678210251</v>
+        <v>13.82148897709166</v>
       </c>
       <c r="E6" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F6" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.50813582229224</v>
+        <v>8.695072071122489</v>
       </c>
       <c r="D7" t="n">
-        <v>64.48741801585061</v>
+        <v>10.47920542757572</v>
       </c>
       <c r="E7" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F7" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.999195587397</v>
+        <v>6.987369282952012</v>
       </c>
       <c r="D8" t="n">
-        <v>49.59895044157773</v>
+        <v>8.059829446756382</v>
       </c>
       <c r="E8" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F8" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.07420399368704</v>
+        <v>4.237058148974144</v>
       </c>
       <c r="D9" t="n">
-        <v>18.47591709397391</v>
+        <v>3.00233652777076</v>
       </c>
       <c r="E9" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F9" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.75188677550672</v>
+        <v>2.884681601019842</v>
       </c>
       <c r="D10" t="n">
-        <v>22.74400790096675</v>
+        <v>3.695901283907097</v>
       </c>
       <c r="E10" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F10" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.49139672185086</v>
+        <v>3.004851967300765</v>
       </c>
       <c r="D11" t="n">
-        <v>32.96996430366418</v>
+        <v>5.357619199345431</v>
       </c>
       <c r="E11" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F11" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>40.55236113764357</v>
+        <v>6.589758684867081</v>
       </c>
       <c r="D12" t="n">
-        <v>57.84652589668406</v>
+        <v>9.400060458211161</v>
       </c>
       <c r="E12" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F12" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>34.45684903369315</v>
+        <v>5.599237967975136</v>
       </c>
       <c r="D13" t="n">
-        <v>59.9011650101053</v>
+        <v>9.733939314142113</v>
       </c>
       <c r="E13" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F13" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>17.16791471491769</v>
+        <v>2.789786141174125</v>
       </c>
       <c r="D14" t="n">
-        <v>17.34903443741367</v>
+        <v>2.819218096079722</v>
       </c>
       <c r="E14" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F14" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>27.17905206606107</v>
+        <v>4.416595960734925</v>
       </c>
       <c r="D15" t="n">
-        <v>52.73987644530968</v>
+        <v>8.570229922362824</v>
       </c>
       <c r="E15" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F15" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>11.53623300414094</v>
+        <v>1.874637863172903</v>
       </c>
       <c r="D16" t="n">
-        <v>42.74038802773886</v>
+        <v>6.945313054507565</v>
       </c>
       <c r="E16" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F16" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>18.40351873907537</v>
+        <v>2.990571795099747</v>
       </c>
       <c r="D17" t="n">
-        <v>48.72911190535263</v>
+        <v>7.918480684619803</v>
       </c>
       <c r="E17" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F17" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>21.31893240303143</v>
+        <v>3.464326515492608</v>
       </c>
       <c r="D18" t="n">
-        <v>52.38550898293007</v>
+        <v>8.512645209726136</v>
       </c>
       <c r="E18" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F18" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>40.24202523438414</v>
+        <v>6.539329100587422</v>
       </c>
       <c r="D19" t="n">
-        <v>38.00197736226809</v>
+        <v>6.175321321368564</v>
       </c>
       <c r="E19" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F19" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>46.08624863459726</v>
+        <v>7.489015403122055</v>
       </c>
       <c r="D20" t="n">
-        <v>43.0053452458856</v>
+        <v>6.98836860245641</v>
       </c>
       <c r="E20" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F20" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>44.91506766006967</v>
+        <v>7.298698494761321</v>
       </c>
       <c r="D21" t="n">
-        <v>45.38433660144817</v>
+        <v>7.374954697735328</v>
       </c>
       <c r="E21" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F21" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>23.27771849651451</v>
+        <v>3.782629255683608</v>
       </c>
       <c r="D22" t="n">
-        <v>49.08103290949222</v>
+        <v>7.975667847792486</v>
       </c>
       <c r="E22" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F22" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>37.63398390642246</v>
+        <v>6.115522384793651</v>
       </c>
       <c r="D23" t="n">
-        <v>36.06418060657072</v>
+        <v>5.860429348567742</v>
       </c>
       <c r="E23" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F23" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>27.88894896659665</v>
+        <v>4.531954207071955</v>
       </c>
       <c r="D24" t="n">
-        <v>25.4816565524831</v>
+        <v>4.140769189778505</v>
       </c>
       <c r="E24" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F24" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>20.1884785992039</v>
+        <v>3.280627772370633</v>
       </c>
       <c r="D25" t="n">
-        <v>17.10487569595762</v>
+        <v>2.779542300593113</v>
       </c>
       <c r="E25" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F25" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>47.03074722087732</v>
+        <v>7.642496423392564</v>
       </c>
       <c r="D26" t="n">
-        <v>52.2718958679991</v>
+        <v>8.494183078549854</v>
       </c>
       <c r="E26" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F26" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>36.35522207608062</v>
+        <v>5.907723587363101</v>
       </c>
       <c r="D27" t="n">
-        <v>66.69573212315048</v>
+        <v>10.83805647001195</v>
       </c>
       <c r="E27" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F27" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>10.20398909571533</v>
+        <v>1.658148228053741</v>
       </c>
       <c r="D28" t="n">
-        <v>7.111364585395239</v>
+        <v>1.155596745126726</v>
       </c>
       <c r="E28" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F28" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>39.65384084709399</v>
+        <v>6.443749137652773</v>
       </c>
       <c r="D29" t="n">
-        <v>39.62948544956845</v>
+        <v>6.439791385554873</v>
       </c>
       <c r="E29" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F29" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>16.69551072273117</v>
+        <v>2.713020492443816</v>
       </c>
       <c r="D30" t="n">
-        <v>16.70731741032116</v>
+        <v>2.714939079177188</v>
       </c>
       <c r="E30" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F30" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>2.188635067065801</v>
+        <v>0.3556531983981927</v>
       </c>
       <c r="D31" t="n">
-        <v>2.188635067065801</v>
+        <v>0.3556531983981927</v>
       </c>
       <c r="E31" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F31" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>13.49456844796083</v>
+        <v>2.192867372793634</v>
       </c>
       <c r="D32" t="n">
-        <v>13.08856754705104</v>
+        <v>2.126892226395794</v>
       </c>
       <c r="E32" t="n">
-        <v>15.39618834614682</v>
+        <v>2.501880606248858</v>
       </c>
       <c r="F32" t="n">
-        <v>19.80626605094584</v>
+        <v>3.218518233278699</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
